--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
@@ -15313,7 +15313,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cobertura APS de vejez</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="695">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
     <t xml:space="preserve">11202</t>
@@ -397,18 +397,18 @@
     <t xml:space="preserve">Quinta de Tilcoco</t>
   </si>
   <si>
+    <t xml:space="preserve">5304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
     <t xml:space="preserve">7406</t>
   </si>
   <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">5304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
     <t xml:space="preserve">6109</t>
   </si>
   <si>
@@ -502,18 +502,18 @@
     <t xml:space="preserve">7105</t>
   </si>
   <si>
+    <t xml:space="preserve">6105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doñihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">7201</t>
   </si>
   <si>
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
-    <t xml:space="preserve">6105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doñihue</t>
-  </si>
-  <si>
     <t xml:space="preserve">7302</t>
   </si>
   <si>
@@ -532,18 +532,18 @@
     <t xml:space="preserve">La Granja</t>
   </si>
   <si>
+    <t xml:space="preserve">6206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paredones</t>
+  </si>
+  <si>
     <t xml:space="preserve">7107</t>
   </si>
   <si>
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
-    <t xml:space="preserve">6206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paredones</t>
-  </si>
-  <si>
     <t xml:space="preserve">7405</t>
   </si>
   <si>
@@ -724,18 +724,18 @@
     <t xml:space="preserve">Casablanca</t>
   </si>
   <si>
+    <t xml:space="preserve">5601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
     <t xml:space="preserve">13504</t>
   </si>
   <si>
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">5601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
     <t xml:space="preserve">13125</t>
   </si>
   <si>
@@ -2056,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:28</t>
+    <t xml:space="preserve">2026-07-30 15:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2068,16 +2068,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_p_aps_a_2021.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura APS de vejez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -4170,10 +4179,10 @@
         <v>2021</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>126</v>
@@ -4202,10 +4211,10 @@
         <v>2021</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>128</v>
@@ -4746,10 +4755,10 @@
         <v>2021</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>161</v>
@@ -4778,10 +4787,10 @@
         <v>2021</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4906,10 +4915,10 @@
         <v>2021</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
@@ -4938,10 +4947,10 @@
         <v>2021</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>173</v>
@@ -5930,10 +5939,10 @@
         <v>2021</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>235</v>
@@ -5962,10 +5971,10 @@
         <v>2021</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>237</v>
@@ -12890,23 +12899,23 @@
         <v>684</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -12921,28 +12930,28 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -12951,7 +12960,7 @@
         <v>2021</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
@@ -2056,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:58</t>
+    <t xml:space="preserve">2026-09-07 13:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2021.xlsx
@@ -2056,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:11</t>
+    <t xml:space="preserve">2026-09-08 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
